--- a/01_Poziadavky/role-systemu.xlsx
+++ b/01_Poziadavky/role-systemu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Papo\source\repos\Rocnikovy_stick_fight\dokumentacia\Stickops\01_Poziadavky\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C876E0D-9D2A-4C9D-9062-CAF1044176EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B5B0375-D86B-40B4-ADB8-09AAD9EE7300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{785DF48F-A35E-4059-87DC-13D123CCB45F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3A44FD9-3C9B-4793-998D-83A35736C76B}"/>
   </bookViews>
   <sheets>
     <sheet name="Roly" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -71,10 +71,10 @@
     <t>Hrá hru: ovláda menu, bojuje proti AI, hrá kampaň, vyberá finisher, mení nastavenia.</t>
   </si>
   <si>
-    <t>UC-001 – UC-006, UC-011 – UC-013</t>
-  </si>
-  <si>
-    <t>Stickops.exe – klávesnica, myš, gamepad</t>
+    <t>UC-001 – UC-016, UC-021</t>
+  </si>
+  <si>
+    <t>Stickops.exe</t>
   </si>
   <si>
     <t>R-02</t>
@@ -86,13 +86,10 @@
     <t>Sekundárny (človek)</t>
   </si>
   <si>
-    <t>Pripojí sa na tej istej klávesnici alebo gamepade v rýchlom zápase a ovláda druhú postavu. Menu neovláda.</t>
-  </si>
-  <si>
-    <t>UC-004</t>
-  </si>
-  <si>
-    <t>Stickops.exe – šípky, Num klávesy, gamepad</t>
+    <t>Pripojí sa na tom istom počítači v rýchlom zápase a ovláda druhú postavu. Menu neovláda.</t>
+  </si>
+  <si>
+    <t>UC-012, UC-002 – UC-010</t>
   </si>
   <si>
     <t>R-03</t>
@@ -104,10 +101,10 @@
     <t>Dizajnér alebo moddér: upravuje a pridáva útoky, arény, finishery, kampaň a osobnosti AI v súboroch JSON.</t>
   </si>
   <si>
-    <t>UC-007 – UC-009</t>
-  </si>
-  <si>
-    <t>textový editor, F5 v hre, stick_cli validate</t>
+    <t>UC-017 – UC-019</t>
+  </si>
+  <si>
+    <t>textový editor, stick_cli validate</t>
   </si>
   <si>
     <t>R-04</t>
@@ -119,7 +116,7 @@
     <t>Trénuje bossov, robí turnaje osobností a ukladá natrénované modely do hry.</t>
   </si>
   <si>
-    <t>UC-010</t>
+    <t>UC-020</t>
   </si>
   <si>
     <t>stick_trainer.exe, stick_cli.exe, TRENER.bat, Python</t>
@@ -137,7 +134,7 @@
     <t>Počítačom riadený bojovník (skriptovaná osobnosť alebo natrénovaná sieť), posiela rovnaké povely ako hráč.</t>
   </si>
   <si>
-    <t>UC-001, UC-002, UC-005, UC-010</t>
+    <t>UC-001 – UC-010, UC-013, UC-020</t>
   </si>
   <si>
     <t>interné rozhranie AiOpponent</t>
@@ -547,7 +544,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DD35CE-65FE-4E54-932D-8ABE6232D17B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AE8B258-8C82-448E-8E73-7D0589DE3F87}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -616,67 +613,67 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
